--- a/data/Delstidue 1/Resultater_Delstudie1_Origami_NY.xlsx
+++ b/data/Delstidue 1/Resultater_Delstudie1_Origami_NY.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ramboll-my.sharepoint.com/personal/ahmad_rezaie_ramboll_no/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="371" documentId="8_{8565D8CC-E97C-49AF-AA88-8F9D5EE4E15B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9978D8F1-981B-49DF-BFAC-F6930BD4B62D}"/>
+  <xr:revisionPtr revIDLastSave="406" documentId="8_{8565D8CC-E97C-49AF-AA88-8F9D5EE4E15B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5AB86B7D-842C-4D1D-9EAF-D04FCCE8A8E4}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1965" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-1965" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rådata" sheetId="1" r:id="rId1"/>
@@ -811,7 +811,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1050,52 +1050,51 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2587,7 +2586,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>2</c:v>
@@ -2692,7 +2691,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>7</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>5</c:v>
@@ -5450,19 +5449,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="101" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
-      <c r="H1" s="93"/>
-      <c r="I1" s="93"/>
-      <c r="J1" s="93"/>
-      <c r="K1" s="93"/>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
       <c r="L1" s="40"/>
       <c r="M1" s="40"/>
       <c r="N1" s="40"/>
@@ -5480,10 +5479,10 @@
       <c r="Z1" s="40"/>
     </row>
     <row r="2" spans="1:26" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="92" t="s">
+      <c r="A2" s="100" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="92"/>
+      <c r="B2" s="100"/>
       <c r="C2" s="33" t="s">
         <v>2</v>
       </c>
@@ -5500,18 +5499,18 @@
       <c r="A3" s="29"/>
       <c r="B3" s="29"/>
       <c r="C3" s="34"/>
-      <c r="D3" s="90" t="s">
+      <c r="D3" s="98" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="90"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="91" t="s">
+      <c r="E3" s="98"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="98"/>
+      <c r="H3" s="99" t="s">
         <v>49</v>
       </c>
-      <c r="I3" s="91"/>
-      <c r="J3" s="91"/>
-      <c r="K3" s="91"/>
+      <c r="I3" s="99"/>
+      <c r="J3" s="99"/>
+      <c r="K3" s="99"/>
     </row>
     <row r="4" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="30" t="s">
@@ -5549,19 +5548,19 @@
       </c>
     </row>
     <row r="5" spans="1:26" s="22" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="89" t="s">
+      <c r="A5" s="97" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="89"/>
-      <c r="K5" s="89"/>
+      <c r="B5" s="97"/>
+      <c r="C5" s="97"/>
+      <c r="D5" s="97"/>
+      <c r="E5" s="97"/>
+      <c r="F5" s="97"/>
+      <c r="G5" s="97"/>
+      <c r="H5" s="97"/>
+      <c r="I5" s="97"/>
+      <c r="J5" s="97"/>
+      <c r="K5" s="97"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
@@ -5809,11 +5808,11 @@
       </c>
     </row>
     <row r="13" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="86" t="s">
+      <c r="A13" s="94" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="86"/>
-      <c r="C13" s="86"/>
+      <c r="B13" s="94"/>
+      <c r="C13" s="94"/>
       <c r="D13" s="25">
         <f t="shared" ref="D13:K13" si="0">COUNTIF(D6:D12,"J")</f>
         <v>4</v>
@@ -5848,11 +5847,11 @@
       </c>
     </row>
     <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="87" t="s">
+      <c r="A14" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="87"/>
-      <c r="C14" s="87"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="95"/>
       <c r="D14" s="26">
         <f t="shared" ref="D14:K14" si="1">COUNTIF(D6:D12,"N")</f>
         <v>3</v>
@@ -5887,11 +5886,11 @@
       </c>
     </row>
     <row r="15" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="88" t="s">
+      <c r="A15" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="88"/>
-      <c r="C15" s="88"/>
+      <c r="B15" s="96"/>
+      <c r="C15" s="96"/>
       <c r="D15" s="27">
         <v>7</v>
       </c>
@@ -5918,11 +5917,11 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="88" t="s">
+      <c r="A16" s="96" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="88"/>
-      <c r="C16" s="88"/>
+      <c r="B16" s="96"/>
+      <c r="C16" s="96"/>
       <c r="D16" s="28">
         <f>IFERROR(D13/D15,0)</f>
         <v>0.5714285714285714</v>
@@ -5957,19 +5956,19 @@
       </c>
     </row>
     <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="89" t="s">
+      <c r="A18" s="97" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="89"/>
-      <c r="C18" s="89"/>
-      <c r="D18" s="89"/>
-      <c r="E18" s="89"/>
-      <c r="F18" s="89"/>
-      <c r="G18" s="89"/>
-      <c r="H18" s="89"/>
-      <c r="I18" s="89"/>
-      <c r="J18" s="89"/>
-      <c r="K18" s="89"/>
+      <c r="B18" s="97"/>
+      <c r="C18" s="97"/>
+      <c r="D18" s="97"/>
+      <c r="E18" s="97"/>
+      <c r="F18" s="97"/>
+      <c r="G18" s="97"/>
+      <c r="H18" s="97"/>
+      <c r="I18" s="97"/>
+      <c r="J18" s="97"/>
+      <c r="K18" s="97"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
@@ -6217,11 +6216,11 @@
       </c>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="86" t="s">
+      <c r="A26" s="94" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="86"/>
-      <c r="C26" s="86"/>
+      <c r="B26" s="94"/>
+      <c r="C26" s="94"/>
       <c r="D26" s="25">
         <f t="shared" ref="D26:K26" si="3">COUNTIF(D19:D25,"J")</f>
         <v>3</v>
@@ -6256,11 +6255,11 @@
       </c>
     </row>
     <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="87" t="s">
+      <c r="A27" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="87"/>
-      <c r="C27" s="87"/>
+      <c r="B27" s="95"/>
+      <c r="C27" s="95"/>
       <c r="D27" s="26">
         <f t="shared" ref="D27:K27" si="4">COUNTIF(D19:D25,"N")</f>
         <v>4</v>
@@ -6295,11 +6294,11 @@
       </c>
     </row>
     <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="88" t="s">
+      <c r="A28" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="88"/>
-      <c r="C28" s="88"/>
+      <c r="B28" s="96"/>
+      <c r="C28" s="96"/>
       <c r="D28" s="27" t="s">
         <v>24</v>
       </c>
@@ -6326,11 +6325,11 @@
       </c>
     </row>
     <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="88" t="s">
+      <c r="A29" s="96" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="88"/>
-      <c r="C29" s="88"/>
+      <c r="B29" s="96"/>
+      <c r="C29" s="96"/>
       <c r="D29" s="28">
         <f t="shared" ref="D29:K29" si="5">IFERROR(D26/D28,0)</f>
         <v>0.42857142857142855</v>
@@ -6365,19 +6364,19 @@
       </c>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="89" t="s">
+      <c r="A31" s="97" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="89"/>
-      <c r="C31" s="89"/>
-      <c r="D31" s="89"/>
-      <c r="E31" s="89"/>
-      <c r="F31" s="89"/>
-      <c r="G31" s="89"/>
-      <c r="H31" s="89"/>
-      <c r="I31" s="89"/>
-      <c r="J31" s="89"/>
-      <c r="K31" s="89"/>
+      <c r="B31" s="97"/>
+      <c r="C31" s="97"/>
+      <c r="D31" s="97"/>
+      <c r="E31" s="97"/>
+      <c r="F31" s="97"/>
+      <c r="G31" s="97"/>
+      <c r="H31" s="97"/>
+      <c r="I31" s="97"/>
+      <c r="J31" s="97"/>
+      <c r="K31" s="97"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
@@ -6600,7 +6599,7 @@
         <v>25</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>45</v>
@@ -6625,14 +6624,14 @@
       </c>
     </row>
     <row r="39" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="86" t="s">
+      <c r="A39" s="94" t="s">
         <v>26</v>
       </c>
-      <c r="B39" s="86"/>
-      <c r="C39" s="86"/>
+      <c r="B39" s="94"/>
+      <c r="C39" s="94"/>
       <c r="D39" s="25">
         <f t="shared" ref="D39:K39" si="6">COUNTIF(D32:D38,"J")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" s="8">
         <f t="shared" si="6"/>
@@ -6664,14 +6663,14 @@
       </c>
     </row>
     <row r="40" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="87" t="s">
+      <c r="A40" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="B40" s="87"/>
-      <c r="C40" s="87"/>
+      <c r="B40" s="95"/>
+      <c r="C40" s="95"/>
       <c r="D40" s="26">
         <f>COUNTIF(D32:D38,"N")</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E40" s="9">
         <f t="shared" ref="E40:K40" si="7">COUNTIF(E32:E38,"N")</f>
@@ -6703,11 +6702,11 @@
       </c>
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="88" t="s">
+      <c r="A41" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="B41" s="88"/>
-      <c r="C41" s="88"/>
+      <c r="B41" s="96"/>
+      <c r="C41" s="96"/>
       <c r="D41" s="27" t="s">
         <v>24</v>
       </c>
@@ -6734,14 +6733,14 @@
       </c>
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="88" t="s">
+      <c r="A42" s="96" t="s">
         <v>29</v>
       </c>
-      <c r="B42" s="88"/>
-      <c r="C42" s="88"/>
+      <c r="B42" s="96"/>
+      <c r="C42" s="96"/>
       <c r="D42" s="28">
         <f t="shared" ref="D42:K42" si="8">IFERROR(D39/D41,0)</f>
-        <v>0</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="E42" s="11">
         <f t="shared" si="8"/>
@@ -6812,191 +6811,191 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D1" s="99" t="s">
+      <c r="D1" s="102" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99" t="s">
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102" t="s">
         <v>49</v>
       </c>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
     </row>
     <row r="2" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C2" s="100" t="s">
+      <c r="C2" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="97" t="s">
+      <c r="D2" s="87" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="97" t="s">
+      <c r="E2" s="87" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="97" t="s">
+      <c r="F2" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="97" t="s">
+      <c r="G2" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="97" t="s">
+      <c r="H2" s="87" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="97" t="s">
+      <c r="I2" s="87" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="97" t="s">
+      <c r="J2" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="97" t="s">
+      <c r="K2" s="87" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C3" s="97" t="s">
+      <c r="C3" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="98">
+      <c r="D3" s="88">
         <v>4</v>
       </c>
-      <c r="E3" s="98">
+      <c r="E3" s="88">
         <v>3</v>
       </c>
-      <c r="F3" s="98">
+      <c r="F3" s="88">
         <v>3</v>
       </c>
-      <c r="G3" s="98">
+      <c r="G3" s="88">
         <v>3</v>
       </c>
-      <c r="H3" s="98">
+      <c r="H3" s="88">
         <v>6</v>
       </c>
-      <c r="I3" s="98">
+      <c r="I3" s="88">
         <v>5</v>
       </c>
-      <c r="J3" s="98">
+      <c r="J3" s="88">
         <v>7</v>
       </c>
-      <c r="K3" s="98">
+      <c r="K3" s="88">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C4" s="97" t="s">
+      <c r="C4" s="87" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="98">
+      <c r="D4" s="88">
         <v>3</v>
       </c>
-      <c r="E4" s="98">
+      <c r="E4" s="88">
         <v>4</v>
       </c>
-      <c r="F4" s="98">
+      <c r="F4" s="88">
         <v>4</v>
       </c>
-      <c r="G4" s="98">
+      <c r="G4" s="88">
         <v>4</v>
       </c>
-      <c r="H4" s="98">
+      <c r="H4" s="88">
         <v>1</v>
       </c>
-      <c r="I4" s="98">
+      <c r="I4" s="88">
         <v>2</v>
       </c>
-      <c r="J4" s="98">
+      <c r="J4" s="88">
         <v>0</v>
       </c>
-      <c r="K4" s="98">
+      <c r="K4" s="88">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B9" s="104"/>
+      <c r="B9" s="93"/>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B10" s="104"/>
+      <c r="B10" s="93"/>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B11" s="104"/>
+      <c r="B11" s="93"/>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B12" s="104"/>
+      <c r="B12" s="93"/>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B13" s="104"/>
+      <c r="B13" s="93"/>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B14" s="104"/>
+      <c r="B14" s="93"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B15" s="104"/>
-      <c r="D15" s="96"/>
-      <c r="E15" s="96"/>
-      <c r="F15" s="96"/>
-      <c r="G15" s="96"/>
-      <c r="H15" s="96"/>
-      <c r="I15" s="96"/>
-      <c r="J15" s="96"/>
-      <c r="K15" s="96"/>
+      <c r="B15" s="93"/>
+      <c r="D15" s="86"/>
+      <c r="E15" s="86"/>
+      <c r="F15" s="86"/>
+      <c r="G15" s="86"/>
+      <c r="H15" s="86"/>
+      <c r="I15" s="86"/>
+      <c r="J15" s="86"/>
+      <c r="K15" s="86"/>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B16" s="104"/>
+      <c r="B16" s="93"/>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="104"/>
+      <c r="B17" s="93"/>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="104"/>
+      <c r="B18" s="93"/>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" s="104"/>
+      <c r="B19" s="93"/>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="104"/>
+      <c r="B20" s="93"/>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="104"/>
+      <c r="B21" s="93"/>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B22" s="104"/>
+      <c r="B22" s="93"/>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="104"/>
+      <c r="B23" s="93"/>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B24" s="104"/>
+      <c r="B24" s="93"/>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="104"/>
+      <c r="B25" s="93"/>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B26" s="104"/>
+      <c r="B26" s="93"/>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" s="104"/>
+      <c r="B27" s="93"/>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B28" s="104"/>
+      <c r="B28" s="93"/>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B29" s="104"/>
+      <c r="B29" s="93"/>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B30" s="104"/>
+      <c r="B30" s="93"/>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B31" s="104"/>
+      <c r="B31" s="93"/>
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B32" s="104"/>
+      <c r="B32" s="93"/>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B33" s="104"/>
+      <c r="B33" s="93"/>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B34" s="104"/>
+      <c r="B34" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7019,183 +7018,183 @@
   </cols>
   <sheetData>
     <row r="4" spans="6:14" x14ac:dyDescent="0.25">
-      <c r="G4" s="99" t="s">
+      <c r="G4" s="102" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="99"/>
-      <c r="K4" s="99" t="s">
+      <c r="H4" s="102"/>
+      <c r="I4" s="102"/>
+      <c r="J4" s="102"/>
+      <c r="K4" s="102" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="99"/>
-      <c r="M4" s="99"/>
-      <c r="N4" s="99"/>
+      <c r="L4" s="102"/>
+      <c r="M4" s="102"/>
+      <c r="N4" s="102"/>
     </row>
     <row r="5" spans="6:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F5" s="102" t="s">
+      <c r="F5" s="91" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="101" t="s">
+      <c r="G5" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="H5" s="101" t="s">
+      <c r="H5" s="90" t="s">
         <v>5</v>
       </c>
-      <c r="I5" s="101" t="s">
+      <c r="I5" s="90" t="s">
         <v>6</v>
       </c>
-      <c r="J5" s="101" t="s">
+      <c r="J5" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="101" t="s">
+      <c r="K5" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="L5" s="101" t="s">
+      <c r="L5" s="90" t="s">
         <v>5</v>
       </c>
-      <c r="M5" s="101" t="s">
+      <c r="M5" s="90" t="s">
         <v>6</v>
       </c>
-      <c r="N5" s="101" t="s">
+      <c r="N5" s="90" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="6:14" x14ac:dyDescent="0.25">
-      <c r="F6" s="103" t="s">
+      <c r="F6" s="92" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="98">
+      <c r="G6" s="88">
         <v>3</v>
       </c>
-      <c r="H6" s="98">
+      <c r="H6" s="88">
         <v>3</v>
       </c>
-      <c r="I6" s="98">
+      <c r="I6" s="88">
         <v>2</v>
       </c>
-      <c r="J6" s="98">
+      <c r="J6" s="88">
         <v>3</v>
       </c>
-      <c r="K6" s="98">
+      <c r="K6" s="88">
         <v>7</v>
       </c>
-      <c r="L6" s="98">
+      <c r="L6" s="88">
         <v>7</v>
       </c>
-      <c r="M6" s="98">
+      <c r="M6" s="88">
         <v>7</v>
       </c>
-      <c r="N6" s="98">
+      <c r="N6" s="88">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="6:14" x14ac:dyDescent="0.25">
-      <c r="F7" s="103" t="s">
+      <c r="F7" s="92" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="98">
+      <c r="G7" s="88">
         <v>4</v>
       </c>
-      <c r="H7" s="98">
+      <c r="H7" s="88">
         <v>4</v>
       </c>
-      <c r="I7" s="98">
+      <c r="I7" s="88">
         <v>5</v>
       </c>
-      <c r="J7" s="98">
+      <c r="J7" s="88">
         <v>4</v>
       </c>
-      <c r="K7" s="98">
+      <c r="K7" s="88">
         <v>0</v>
       </c>
-      <c r="L7" s="98">
+      <c r="L7" s="88">
         <v>0</v>
       </c>
-      <c r="M7" s="98">
+      <c r="M7" s="88">
         <v>0</v>
       </c>
-      <c r="N7" s="98">
+      <c r="N7" s="88">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="6:14" x14ac:dyDescent="0.25">
-      <c r="F14" s="104"/>
+      <c r="F14" s="93"/>
     </row>
     <row r="15" spans="6:14" x14ac:dyDescent="0.25">
-      <c r="F15" s="104"/>
+      <c r="F15" s="93"/>
     </row>
     <row r="16" spans="6:14" x14ac:dyDescent="0.25">
-      <c r="F16" s="104"/>
+      <c r="F16" s="93"/>
     </row>
     <row r="17" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F17" s="104"/>
+      <c r="F17" s="93"/>
     </row>
     <row r="18" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F18" s="104"/>
+      <c r="F18" s="93"/>
     </row>
     <row r="19" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F19" s="104"/>
+      <c r="F19" s="93"/>
     </row>
     <row r="20" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F20" s="104"/>
+      <c r="F20" s="93"/>
     </row>
     <row r="21" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F21" s="104"/>
+      <c r="F21" s="93"/>
     </row>
     <row r="22" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F22" s="104"/>
+      <c r="F22" s="93"/>
     </row>
     <row r="23" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F23" s="104"/>
+      <c r="F23" s="93"/>
     </row>
     <row r="24" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F24" s="104"/>
+      <c r="F24" s="93"/>
     </row>
     <row r="25" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F25" s="104"/>
+      <c r="F25" s="93"/>
     </row>
     <row r="26" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F26" s="104"/>
+      <c r="F26" s="93"/>
     </row>
     <row r="27" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F27" s="104"/>
+      <c r="F27" s="93"/>
     </row>
     <row r="28" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F28" s="104"/>
+      <c r="F28" s="93"/>
     </row>
     <row r="29" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F29" s="104"/>
+      <c r="F29" s="93"/>
     </row>
     <row r="30" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F30" s="104"/>
+      <c r="F30" s="93"/>
     </row>
     <row r="31" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F31" s="104"/>
+      <c r="F31" s="93"/>
     </row>
     <row r="32" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F32" s="104"/>
+      <c r="F32" s="93"/>
     </row>
     <row r="33" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F33" s="104"/>
+      <c r="F33" s="93"/>
     </row>
     <row r="34" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F34" s="104"/>
+      <c r="F34" s="93"/>
     </row>
     <row r="35" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F35" s="104"/>
+      <c r="F35" s="93"/>
     </row>
     <row r="36" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F36" s="104"/>
+      <c r="F36" s="93"/>
     </row>
     <row r="37" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F37" s="104"/>
+      <c r="F37" s="93"/>
     </row>
     <row r="38" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F38" s="104"/>
+      <c r="F38" s="93"/>
     </row>
     <row r="39" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F39" s="104"/>
+      <c r="F39" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7216,103 +7215,103 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B2" s="99" t="s">
+      <c r="B2" s="102" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99" t="s">
+      <c r="C2" s="102"/>
+      <c r="D2" s="102"/>
+      <c r="E2" s="102"/>
+      <c r="F2" s="102" t="s">
         <v>49</v>
       </c>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
+      <c r="G2" s="102"/>
+      <c r="H2" s="102"/>
+      <c r="I2" s="102"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="105" t="s">
+      <c r="A3" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="97" t="s">
+      <c r="B3" s="87" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="97" t="s">
+      <c r="C3" s="87" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="97" t="s">
+      <c r="D3" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="97" t="s">
+      <c r="E3" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="97" t="s">
+      <c r="F3" s="87" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="97" t="s">
+      <c r="G3" s="87" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="97" t="s">
+      <c r="H3" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="97" t="s">
+      <c r="I3" s="87" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="98" t="s">
+      <c r="A4" s="88" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="98">
+      <c r="B4" s="88">
+        <v>1</v>
+      </c>
+      <c r="C4" s="88">
+        <v>2</v>
+      </c>
+      <c r="D4" s="88">
+        <v>3</v>
+      </c>
+      <c r="E4" s="88">
+        <v>2</v>
+      </c>
+      <c r="F4" s="88">
+        <v>7</v>
+      </c>
+      <c r="G4" s="88">
+        <v>6</v>
+      </c>
+      <c r="H4" s="88">
+        <v>7</v>
+      </c>
+      <c r="I4" s="88">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="88">
+        <v>6</v>
+      </c>
+      <c r="C5" s="88">
+        <v>5</v>
+      </c>
+      <c r="D5" s="88">
+        <v>4</v>
+      </c>
+      <c r="E5" s="88">
+        <v>5</v>
+      </c>
+      <c r="F5" s="88">
         <v>0</v>
       </c>
-      <c r="C4" s="98">
-        <v>2</v>
-      </c>
-      <c r="D4" s="98">
-        <v>3</v>
-      </c>
-      <c r="E4" s="98">
-        <v>2</v>
-      </c>
-      <c r="F4" s="98">
-        <v>7</v>
-      </c>
-      <c r="G4" s="98">
-        <v>6</v>
-      </c>
-      <c r="H4" s="98">
-        <v>7</v>
-      </c>
-      <c r="I4" s="98">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="98" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="98">
-        <v>7</v>
-      </c>
-      <c r="C5" s="98">
-        <v>5</v>
-      </c>
-      <c r="D5" s="98">
-        <v>4</v>
-      </c>
-      <c r="E5" s="98">
-        <v>5</v>
-      </c>
-      <c r="F5" s="98">
+      <c r="G5" s="88">
+        <v>1</v>
+      </c>
+      <c r="H5" s="88">
         <v>0</v>
       </c>
-      <c r="G5" s="98">
-        <v>1</v>
-      </c>
-      <c r="H5" s="98">
-        <v>0</v>
-      </c>
-      <c r="I5" s="98">
+      <c r="I5" s="88">
         <v>2</v>
       </c>
     </row>
@@ -7340,20 +7339,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="101" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
-      <c r="H1" s="93"/>
-      <c r="I1" s="93"/>
-      <c r="J1" s="93"/>
-      <c r="K1" s="93"/>
-      <c r="L1" s="93"/>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="85"/>
@@ -7425,7 +7424,7 @@
         <v>15</v>
       </c>
       <c r="K3" s="61">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -7465,7 +7464,7 @@
         <v>15</v>
       </c>
       <c r="K4" s="55">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -7505,7 +7504,7 @@
         <v>15</v>
       </c>
       <c r="K5" s="55">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7545,7 +7544,7 @@
         <v>15</v>
       </c>
       <c r="K6" s="47">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -7585,7 +7584,7 @@
         <v>5</v>
       </c>
       <c r="K7" s="61">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -7625,7 +7624,7 @@
         <v>5</v>
       </c>
       <c r="K8" s="55">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -7665,7 +7664,7 @@
         <v>5</v>
       </c>
       <c r="K9" s="55">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7705,7 +7704,7 @@
         <v>5</v>
       </c>
       <c r="K10" s="47">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7752,7 +7751,7 @@
         <v>17</v>
       </c>
       <c r="K12" s="61">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -7792,7 +7791,7 @@
         <v>17</v>
       </c>
       <c r="K13" s="55">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -7832,7 +7831,7 @@
         <v>17</v>
       </c>
       <c r="K14" s="55">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7872,7 +7871,7 @@
         <v>17</v>
       </c>
       <c r="K15" s="47">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -7912,7 +7911,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="61">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -7952,7 +7951,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="55">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -7992,7 +7991,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="55">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8032,7 +8031,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="47">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8052,7 +8051,7 @@
       </c>
       <c r="D21" s="79">
         <f>Rådata!D42</f>
-        <v>0</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="E21" s="79">
         <f>Rådata!E42</f>
@@ -8068,18 +8067,18 @@
       </c>
       <c r="H21" s="64">
         <f t="shared" ref="H21:H28" si="2">AVERAGE(D21:G21)</f>
-        <v>0.24999999999999997</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="I21" s="63">
         <f>Rådata!D39+Rådata!E39+Rådata!F39+Rådata!G39</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J21" s="62">
         <f>Rådata!D40+Rådata!E40+Rådata!F40+Rådata!G40</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K21" s="61">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -8092,7 +8091,7 @@
       </c>
       <c r="D22" s="75">
         <f>Rådata!D42</f>
-        <v>0</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="E22" s="75">
         <f>Rådata!E42</f>
@@ -8108,18 +8107,18 @@
       </c>
       <c r="H22" s="56">
         <f t="shared" si="2"/>
-        <v>0.24999999999999997</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="I22" s="8">
         <f>Rådata!D39+Rådata!E39+Rådata!F39+Rådata!G39</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J22" s="9">
         <f>Rådata!D40+Rådata!E40+Rådata!F40+Rådata!G40</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K22" s="55">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -8132,7 +8131,7 @@
       </c>
       <c r="D23" s="75">
         <f>Rådata!D42</f>
-        <v>0</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="E23" s="75">
         <f>Rådata!E42</f>
@@ -8148,18 +8147,18 @@
       </c>
       <c r="H23" s="56">
         <f t="shared" si="2"/>
-        <v>0.24999999999999997</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="I23" s="8">
         <f>Rådata!D39+Rådata!E39+Rådata!F39+Rådata!G39</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J23" s="9">
         <f>Rådata!D40+Rådata!E40+Rådata!F40+Rådata!G40</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K23" s="55">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8172,7 +8171,7 @@
       </c>
       <c r="D24" s="70">
         <f>Rådata!D42</f>
-        <v>0</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="E24" s="70">
         <f>Rådata!E42</f>
@@ -8188,18 +8187,18 @@
       </c>
       <c r="H24" s="50">
         <f t="shared" si="2"/>
-        <v>0.24999999999999997</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="I24" s="49">
         <f>Rådata!D39+Rådata!E39+Rådata!F39+Rådata!G39</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J24" s="48">
         <f>Rådata!D40+Rådata!E40+Rådata!F40+Rådata!G40</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K24" s="47">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -8239,7 +8238,7 @@
         <v>3</v>
       </c>
       <c r="K25" s="61">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -8279,7 +8278,7 @@
         <v>3</v>
       </c>
       <c r="K26" s="55">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -8319,7 +8318,7 @@
         <v>3</v>
       </c>
       <c r="K27" s="55">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8359,15 +8358,15 @@
         <v>3</v>
       </c>
       <c r="K28" s="47">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="94" t="s">
+      <c r="A31" s="103" t="s">
         <v>52</v>
       </c>
-      <c r="B31" s="94"/>
-      <c r="C31" s="95"/>
+      <c r="B31" s="103"/>
+      <c r="C31" s="104"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="44"/>
@@ -8377,7 +8376,7 @@
       </c>
       <c r="H32" s="45">
         <f>AVERAGE(H3,H4,H5,H6,H12,H13,H14,H15,H21,H22,H23,H24)</f>
-        <v>0.36904761904761901</v>
+        <v>0.38095238095238093</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">

--- a/data/Delstidue 1/Resultater_Delstudie1_Origami_NY.xlsx
+++ b/data/Delstidue 1/Resultater_Delstudie1_Origami_NY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ramboll-my.sharepoint.com/personal/ahmad_rezaie_ramboll_no/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="406" documentId="8_{8565D8CC-E97C-49AF-AA88-8F9D5EE4E15B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5AB86B7D-842C-4D1D-9EAF-D04FCCE8A8E4}"/>
+  <xr:revisionPtr revIDLastSave="407" documentId="8_{8565D8CC-E97C-49AF-AA88-8F9D5EE4E15B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8ACA5C39-F111-49E8-B64F-95246F9678D6}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1965" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-1965" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rådata" sheetId="1" r:id="rId1"/>
@@ -154,9 +154,6 @@
     <t>5. Gå til fanen «Analyse og resultater» for å se gjennomsnittlig Precision per case, modell og samlet</t>
   </si>
   <si>
-    <t>Feltstruktur per case (13 felt totalt, 12 evaluerbare):</t>
-  </si>
-  <si>
     <t>§11-2: Risikoklasse (prompt 1)</t>
   </si>
   <si>
@@ -242,6 +239,9 @@
   </si>
   <si>
     <t>Analyse – Delstudie 1: Origami | Precision per case og modell</t>
+  </si>
+  <si>
+    <t>Feltstruktur per case (7):</t>
   </si>
 </sst>
 </file>
@@ -1062,6 +1062,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1070,21 +1085,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -5449,19 +5449,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="97" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
-      <c r="K1" s="101"/>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="97"/>
+      <c r="I1" s="97"/>
+      <c r="J1" s="97"/>
+      <c r="K1" s="97"/>
       <c r="L1" s="40"/>
       <c r="M1" s="40"/>
       <c r="N1" s="40"/>
@@ -5479,10 +5479,10 @@
       <c r="Z1" s="40"/>
     </row>
     <row r="2" spans="1:26" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="100" t="s">
+      <c r="A2" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="100"/>
+      <c r="B2" s="96"/>
       <c r="C2" s="33" t="s">
         <v>2</v>
       </c>
@@ -5499,28 +5499,28 @@
       <c r="A3" s="29"/>
       <c r="B3" s="29"/>
       <c r="C3" s="34"/>
-      <c r="D3" s="98" t="s">
+      <c r="D3" s="94" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="98"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="98"/>
-      <c r="H3" s="99" t="s">
-        <v>49</v>
-      </c>
-      <c r="I3" s="99"/>
-      <c r="J3" s="99"/>
-      <c r="K3" s="99"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="95" t="s">
+        <v>48</v>
+      </c>
+      <c r="I3" s="95"/>
+      <c r="J3" s="95"/>
+      <c r="K3" s="95"/>
     </row>
     <row r="4" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="35" t="s">
         <v>47</v>
-      </c>
-      <c r="B4" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="35" t="s">
-        <v>48</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>4</v>
@@ -5548,19 +5548,19 @@
       </c>
     </row>
     <row r="5" spans="1:26" s="22" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="97" t="s">
+      <c r="A5" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="97"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
-      <c r="E5" s="97"/>
-      <c r="F5" s="97"/>
-      <c r="G5" s="97"/>
-      <c r="H5" s="97"/>
-      <c r="I5" s="97"/>
-      <c r="J5" s="97"/>
-      <c r="K5" s="97"/>
+      <c r="B5" s="98"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="98"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="98"/>
+      <c r="K5" s="98"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
@@ -5573,28 +5573,28 @@
         <v>11</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I6" s="21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J6" s="21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K6" s="21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
@@ -5608,28 +5608,28 @@
         <v>14</v>
       </c>
       <c r="D7" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>46</v>
-      </c>
       <c r="H7" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -5643,28 +5643,28 @@
         <v>17</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H8" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="K8" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="38.25" x14ac:dyDescent="0.25">
@@ -5678,28 +5678,28 @@
         <v>19</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="I9" s="7" t="s">
-        <v>46</v>
-      </c>
       <c r="J9" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
@@ -5713,28 +5713,28 @@
         <v>21</v>
       </c>
       <c r="D10" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>46</v>
-      </c>
       <c r="F10" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G10" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="H10" s="7" t="s">
-        <v>46</v>
-      </c>
       <c r="I10" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
@@ -5748,28 +5748,28 @@
         <v>23</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I11" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="I11" s="7" t="s">
-        <v>46</v>
-      </c>
       <c r="J11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="K11" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="25.5" x14ac:dyDescent="0.25">
@@ -5783,36 +5783,36 @@
         <v>25</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="94" t="s">
+      <c r="A13" s="99" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="94"/>
-      <c r="C13" s="94"/>
+      <c r="B13" s="99"/>
+      <c r="C13" s="99"/>
       <c r="D13" s="25">
         <f t="shared" ref="D13:K13" si="0">COUNTIF(D6:D12,"J")</f>
         <v>4</v>
@@ -5847,11 +5847,11 @@
       </c>
     </row>
     <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="95" t="s">
+      <c r="A14" s="100" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="95"/>
-      <c r="C14" s="95"/>
+      <c r="B14" s="100"/>
+      <c r="C14" s="100"/>
       <c r="D14" s="26">
         <f t="shared" ref="D14:K14" si="1">COUNTIF(D6:D12,"N")</f>
         <v>3</v>
@@ -5886,11 +5886,11 @@
       </c>
     </row>
     <row r="15" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="96" t="s">
+      <c r="A15" s="101" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="96"/>
-      <c r="C15" s="96"/>
+      <c r="B15" s="101"/>
+      <c r="C15" s="101"/>
       <c r="D15" s="27">
         <v>7</v>
       </c>
@@ -5917,11 +5917,11 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="96" t="s">
+      <c r="A16" s="101" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="96"/>
-      <c r="C16" s="96"/>
+      <c r="B16" s="101"/>
+      <c r="C16" s="101"/>
       <c r="D16" s="28">
         <f>IFERROR(D13/D15,0)</f>
         <v>0.5714285714285714</v>
@@ -5956,19 +5956,19 @@
       </c>
     </row>
     <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="97" t="s">
+      <c r="A18" s="98" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="97"/>
-      <c r="C18" s="97"/>
-      <c r="D18" s="97"/>
-      <c r="E18" s="97"/>
-      <c r="F18" s="97"/>
-      <c r="G18" s="97"/>
-      <c r="H18" s="97"/>
-      <c r="I18" s="97"/>
-      <c r="J18" s="97"/>
-      <c r="K18" s="97"/>
+      <c r="B18" s="98"/>
+      <c r="C18" s="98"/>
+      <c r="D18" s="98"/>
+      <c r="E18" s="98"/>
+      <c r="F18" s="98"/>
+      <c r="G18" s="98"/>
+      <c r="H18" s="98"/>
+      <c r="I18" s="98"/>
+      <c r="J18" s="98"/>
+      <c r="K18" s="98"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
@@ -5981,28 +5981,28 @@
         <v>11</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -6016,28 +6016,28 @@
         <v>14</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -6051,28 +6051,28 @@
         <v>17</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
@@ -6086,28 +6086,28 @@
         <v>19</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E22" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F22" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>46</v>
-      </c>
       <c r="G22" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -6121,28 +6121,28 @@
         <v>21</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -6156,28 +6156,28 @@
         <v>23</v>
       </c>
       <c r="D24" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E24" s="6" t="s">
-        <v>46</v>
-      </c>
       <c r="F24" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
@@ -6191,36 +6191,36 @@
         <v>25</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="94" t="s">
+      <c r="A26" s="99" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="94"/>
-      <c r="C26" s="94"/>
+      <c r="B26" s="99"/>
+      <c r="C26" s="99"/>
       <c r="D26" s="25">
         <f t="shared" ref="D26:K26" si="3">COUNTIF(D19:D25,"J")</f>
         <v>3</v>
@@ -6255,11 +6255,11 @@
       </c>
     </row>
     <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="95" t="s">
+      <c r="A27" s="100" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="95"/>
-      <c r="C27" s="95"/>
+      <c r="B27" s="100"/>
+      <c r="C27" s="100"/>
       <c r="D27" s="26">
         <f t="shared" ref="D27:K27" si="4">COUNTIF(D19:D25,"N")</f>
         <v>4</v>
@@ -6294,11 +6294,11 @@
       </c>
     </row>
     <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="96" t="s">
+      <c r="A28" s="101" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="96"/>
-      <c r="C28" s="96"/>
+      <c r="B28" s="101"/>
+      <c r="C28" s="101"/>
       <c r="D28" s="27" t="s">
         <v>24</v>
       </c>
@@ -6325,11 +6325,11 @@
       </c>
     </row>
     <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="96" t="s">
+      <c r="A29" s="101" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="96"/>
-      <c r="C29" s="96"/>
+      <c r="B29" s="101"/>
+      <c r="C29" s="101"/>
       <c r="D29" s="28">
         <f t="shared" ref="D29:K29" si="5">IFERROR(D26/D28,0)</f>
         <v>0.42857142857142855</v>
@@ -6364,19 +6364,19 @@
       </c>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="97" t="s">
+      <c r="A31" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="97"/>
-      <c r="C31" s="97"/>
-      <c r="D31" s="97"/>
-      <c r="E31" s="97"/>
-      <c r="F31" s="97"/>
-      <c r="G31" s="97"/>
-      <c r="H31" s="97"/>
-      <c r="I31" s="97"/>
-      <c r="J31" s="97"/>
-      <c r="K31" s="97"/>
+      <c r="B31" s="98"/>
+      <c r="C31" s="98"/>
+      <c r="D31" s="98"/>
+      <c r="E31" s="98"/>
+      <c r="F31" s="98"/>
+      <c r="G31" s="98"/>
+      <c r="H31" s="98"/>
+      <c r="I31" s="98"/>
+      <c r="J31" s="98"/>
+      <c r="K31" s="98"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
@@ -6389,28 +6389,28 @@
         <v>11</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F32" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G32" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="G32" s="6" t="s">
-        <v>46</v>
-      </c>
       <c r="H32" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K32" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -6424,28 +6424,28 @@
         <v>14</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -6459,28 +6459,28 @@
         <v>17</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H34" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I34" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="I34" s="7" t="s">
-        <v>46</v>
-      </c>
       <c r="J34" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="K34" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="K34" s="7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
@@ -6494,28 +6494,28 @@
         <v>19</v>
       </c>
       <c r="D35" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -6529,28 +6529,28 @@
         <v>21</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K36" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -6564,28 +6564,28 @@
         <v>23</v>
       </c>
       <c r="D37" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H37" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="K37" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="I37" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="J37" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="K37" s="7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
@@ -6599,36 +6599,36 @@
         <v>25</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K38" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="94" t="s">
+      <c r="A39" s="99" t="s">
         <v>26</v>
       </c>
-      <c r="B39" s="94"/>
-      <c r="C39" s="94"/>
+      <c r="B39" s="99"/>
+      <c r="C39" s="99"/>
       <c r="D39" s="25">
         <f t="shared" ref="D39:K39" si="6">COUNTIF(D32:D38,"J")</f>
         <v>1</v>
@@ -6663,11 +6663,11 @@
       </c>
     </row>
     <row r="40" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="95" t="s">
+      <c r="A40" s="100" t="s">
         <v>27</v>
       </c>
-      <c r="B40" s="95"/>
-      <c r="C40" s="95"/>
+      <c r="B40" s="100"/>
+      <c r="C40" s="100"/>
       <c r="D40" s="26">
         <f>COUNTIF(D32:D38,"N")</f>
         <v>6</v>
@@ -6702,11 +6702,11 @@
       </c>
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="96" t="s">
+      <c r="A41" s="101" t="s">
         <v>28</v>
       </c>
-      <c r="B41" s="96"/>
-      <c r="C41" s="96"/>
+      <c r="B41" s="101"/>
+      <c r="C41" s="101"/>
       <c r="D41" s="27" t="s">
         <v>24</v>
       </c>
@@ -6733,11 +6733,11 @@
       </c>
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="96" t="s">
+      <c r="A42" s="101" t="s">
         <v>29</v>
       </c>
-      <c r="B42" s="96"/>
-      <c r="C42" s="96"/>
+      <c r="B42" s="101"/>
+      <c r="C42" s="101"/>
       <c r="D42" s="28">
         <f t="shared" ref="D42:K42" si="8">IFERROR(D39/D41,0)</f>
         <v>0.14285714285714285</v>
@@ -6773,16 +6773,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="H3:K3"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A18:K18"/>
     <mergeCell ref="A39:C39"/>
     <mergeCell ref="A40:C40"/>
     <mergeCell ref="A41:C41"/>
@@ -6792,6 +6782,16 @@
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A31:K31"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="H3:K3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A5:K5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6818,7 +6818,7 @@
       <c r="F1" s="102"/>
       <c r="G1" s="102"/>
       <c r="H1" s="102" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I1" s="102"/>
       <c r="J1" s="102"/>
@@ -7025,7 +7025,7 @@
       <c r="I4" s="102"/>
       <c r="J4" s="102"/>
       <c r="K4" s="102" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L4" s="102"/>
       <c r="M4" s="102"/>
@@ -7222,7 +7222,7 @@
       <c r="D2" s="102"/>
       <c r="E2" s="102"/>
       <c r="F2" s="102" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G2" s="102"/>
       <c r="H2" s="102"/>
@@ -7339,58 +7339,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="101" t="s">
-        <v>66</v>
-      </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101"/>
+      <c r="A1" s="97" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="97"/>
+      <c r="I1" s="97"/>
+      <c r="J1" s="97"/>
+      <c r="K1" s="97"/>
+      <c r="L1" s="97"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="85"/>
       <c r="B2" s="84" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C2" s="84" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D2" s="84" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E2" s="84" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F2" s="84" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G2" s="84" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H2" s="84" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I2" s="84" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J2" s="84" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K2" s="84" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="73"/>
       <c r="B3" s="81" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C3" s="80" t="s">
         <v>3</v>
@@ -7430,7 +7430,7 @@
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="73"/>
       <c r="B4" s="77" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C4" s="76" t="s">
         <v>3</v>
@@ -7470,7 +7470,7 @@
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="73"/>
       <c r="B5" s="77" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C5" s="76" t="s">
         <v>3</v>
@@ -7510,7 +7510,7 @@
     <row r="6" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="73"/>
       <c r="B6" s="72" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C6" s="71" t="s">
         <v>3</v>
@@ -7550,10 +7550,10 @@
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="43"/>
       <c r="B7" s="68" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C7" s="67" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D7" s="66">
         <f>Rådata!H16</f>
@@ -7590,10 +7590,10 @@
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="43"/>
       <c r="B8" s="60" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D8" s="58">
         <f>Rådata!H16</f>
@@ -7630,10 +7630,10 @@
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="43"/>
       <c r="B9" s="60" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C9" s="59" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" s="58">
         <f>Rådata!H16</f>
@@ -7670,10 +7670,10 @@
     <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="43"/>
       <c r="B10" s="54" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C10" s="53" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D10" s="52">
         <f>Rådata!H16</f>
@@ -7717,7 +7717,7 @@
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="43"/>
       <c r="B12" s="68" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C12" s="80" t="s">
         <v>3</v>
@@ -7757,7 +7757,7 @@
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="43"/>
       <c r="B13" s="60" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C13" s="76" t="s">
         <v>3</v>
@@ -7797,7 +7797,7 @@
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="43"/>
       <c r="B14" s="60" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C14" s="76" t="s">
         <v>3</v>
@@ -7837,7 +7837,7 @@
     <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="43"/>
       <c r="B15" s="54" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C15" s="71" t="s">
         <v>3</v>
@@ -7877,10 +7877,10 @@
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="73"/>
       <c r="B16" s="81" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C16" s="67" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D16" s="66">
         <f>Rådata!H29</f>
@@ -7917,10 +7917,10 @@
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="73"/>
       <c r="B17" s="77" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C17" s="59" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D17" s="58">
         <f>Rådata!H29</f>
@@ -7957,10 +7957,10 @@
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="73"/>
       <c r="B18" s="77" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D18" s="58">
         <f>Rådata!H29</f>
@@ -7997,10 +7997,10 @@
     <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="73"/>
       <c r="B19" s="72" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C19" s="53" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D19" s="52">
         <f>Rådata!H29</f>
@@ -8044,7 +8044,7 @@
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="73"/>
       <c r="B21" s="81" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C21" s="80" t="s">
         <v>3</v>
@@ -8084,7 +8084,7 @@
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="73"/>
       <c r="B22" s="77" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C22" s="76" t="s">
         <v>3</v>
@@ -8124,7 +8124,7 @@
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="73"/>
       <c r="B23" s="77" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C23" s="76" t="s">
         <v>3</v>
@@ -8164,7 +8164,7 @@
     <row r="24" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="73"/>
       <c r="B24" s="72" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C24" s="71" t="s">
         <v>3</v>
@@ -8204,10 +8204,10 @@
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="43"/>
       <c r="B25" s="68" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C25" s="67" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D25" s="66">
         <f>Rådata!H42</f>
@@ -8244,10 +8244,10 @@
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="43"/>
       <c r="B26" s="60" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C26" s="59" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D26" s="58">
         <f>Rådata!H42</f>
@@ -8284,10 +8284,10 @@
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="43"/>
       <c r="B27" s="60" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C27" s="59" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D27" s="58">
         <f>Rådata!H42</f>
@@ -8324,10 +8324,10 @@
     <row r="28" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="43"/>
       <c r="B28" s="54" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C28" s="53" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D28" s="52">
         <f>Rådata!H42</f>
@@ -8363,7 +8363,7 @@
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="103" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B31" s="103"/>
       <c r="C31" s="104"/>
@@ -8383,7 +8383,7 @@
       <c r="A33" s="44"/>
       <c r="B33" s="43"/>
       <c r="C33" s="42" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H33" s="41">
         <f>AVERAGE(H7,H8,H9,H10,H16,H17,H18,H19,H25,H26,H27,H28)</f>
@@ -8489,42 +8489,42 @@
     </row>
     <row r="8" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="16" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
